--- a/marketing-repository/data/BSymbolic_Marketing_Master_Expanded.xlsx
+++ b/marketing-repository/data/BSymbolic_Marketing_Master_Expanded.xlsx
@@ -34,7 +34,9 @@
     <sheet name="Branding and Creative" sheetId="25" state="visible" r:id="rId25"/>
     <sheet name="B2B and Account-Based" sheetId="26" state="visible" r:id="rId26"/>
     <sheet name="Cause and Community" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="PBC Priority Playbook" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="US Metro Reference" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Metro OOH Companies" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="PBC Priority Playbook" sheetId="30" state="visible" r:id="rId30"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master List'!$A$2:$G$1118</definedName>
@@ -63,6 +65,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'Branding and Creative'!$A$2:$F$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'B2B and Account-Based'!$A$2:$F$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'Cause and Community'!$A$2:$F$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'US Metro Reference'!$A$2:$J$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'Metro OOH Companies'!$A$2:$H$112</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -544,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -656,6 +660,18 @@
       <c r="B11" s="3" t="inlineStr">
         <is>
           <t>This master extends the original OOH/local menu into ALL marketing: Email/SMS, Content &amp; SEO, Video/CTV, Audio, Influencer, Loyalty, Web/CRO, Sales Enablement, Analytics/MarTech, Branding, B2B/ABM and Cause/CSR. Trades Relevance ratings keep the Palm Beach home-services lens.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>US Metros</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>US Metro Reference = 42 largest markets with DMA rank, population, OOH rate band, # billboard operators, dominant newspaper &amp; business journal. Metro OOH Companies = 110 scraped billboard/OOH operators by metro. Turns the tactic menu into a US market reference.</t>
         </is>
       </c>
     </row>
@@ -53820,446 +53836,6209 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="55" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>B. SYMBOLIC — PALM BEACH COUNTY PRIORITY PLAYBOOK</t>
+          <t>US METRO MARKETING REFERENCE - 42 MARKETS</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Why it wins for you</t>
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Metro</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>DMA Rank (approx)</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Metro Pop</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>OOH Rate ($/mo)</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>OOH Ops (#)</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Major Newspaper</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Business Journal</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Market Notes</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>1 - Foundation</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Google Business Profile + Reviews</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Search/Local</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>FREE, drives the map pack. Non-negotiable base.</t>
+      <c r="A3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>19.9M</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>$3,000-$50,000</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>The New York Times / NY Post / Daily News</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>Crain's New York Business</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>Times Square spectaculars $10,000 to $1,000,000+/mo; Manhattan digital $15k–$50k; outer-borough static $3k–$8k.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>1 - Foundation</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Google Local Service Ads (LSA)</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Search/Local</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Best trades lead quality; you're license/insurance-qualified.</t>
+      <c r="A4" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>13.0M</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>$2,500-$40,000</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>Los Angeles Times</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>Los Angeles Business Journal</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>Iconic Sunset Strip bulletins command a large multiple of comparable units 30 mi east.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>1 - Foundation</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>CallRail call tracking</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Tools</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Attribute every call to the campaign that drove it.</t>
+      <c r="A5" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>9.4M</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>$2,000-$25,000</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Chicago Tribune / Sun-Times</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Crain's Chicago Business</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Premium expressway (Kennedy/Dan Ryan) and Loop digital displays at the high end.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>2 - Relationships</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Property manager / HOA agreements</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Partnership</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Recurring commercial - highest LTV in PBC.</t>
+      <c r="A6" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>4.6M (Bay CSA ~9.7M)</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>$2,500-$30,000</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>San Francisco Chronicle</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>San Francisco Business Times</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Bay Area (SF/Oakland/San Jose); tech-driven demand and scarce inventory keep rates high.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>2 - Relationships</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Realtor + home-inspector + restoration referrals</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Partnership</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Renewable, pre-qualified lead sources for free.</t>
+      <c r="A7" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>6.4M</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>$1,500-$16,000</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>The Atlanta Journal-Constitution</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Atlanta Business Chronicle</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Connector/I-285 'Perimeter' corridors; large billboard-friendly metro.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>2 - Relationships</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Water-filtration certified-installer status</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Partnership</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Qualified inbound + co-marketing on your water side.</t>
+      <c r="A8" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Washington DC</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>6.3M</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>$2,000-$20,000</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>The Washington Post</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>Washington Business Journal</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>Billboards tightly limited in DC proper; value concentrated on MD/VA approaches &amp; transit.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>3 - Local Saturation</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Vehicle wraps + yard signs + door hangers</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Local/OOH</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Cheap saturation in your exact service area. Produce in-house.</t>
+      <c r="A9" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>4.9M</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>$1,800-$18,000</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>The Boston Globe</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Boston Business Journal</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>OUTFRONT #1 with 675+ digital faces; I-93/Mass Pike and tunnel approaches priced highest.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>3 - Local Saturation</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Fridge/emergency magnets + shutoff-valve tags</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Promo</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Year-round visibility; shutoff tags are a unique differentiator.</t>
+      <c r="A10" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>8.1M</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>$1,500-$18,000</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>The Dallas Morning News</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>Dallas Business Journal</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>High-traffic corridors (I-35, LBJ, Central Expwy) priced highest.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>3 - Local Saturation</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Nextdoor + Facebook local Groups</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Social</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Trust-based, near-free, converts like referrals.</t>
+      <c r="A11" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>7.5M</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>$1,500-$15,000</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>Houston Chronicle</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Houston Business Journal</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>Clear Channel alone runs 2,000+ boards across 13 counties (99% of DMA adults).</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>4 - Content Engine</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>City landing pages + Local SEO</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Owned</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>One page per PBC city, each in its own map pack.</t>
+      <c r="A12" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Miami</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>6.2M</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>$1,800-$20,000</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>Miami Herald</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>South Florida Business Journal</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>I-95 / Palmetto / Dolphin Expwy and beach/tourism corridors carry premiums.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>4 - Content Engine</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Interactive tools (Hard Water Map, calculators, quiz)</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Owned</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>You already build these; gate them, feed the CRM.</t>
+      <c r="A13" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>6.2M</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>$1,500-$12,000</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>The Philadelphia Inquirer</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Philadelphia Business Journal</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>I-95 / Schuylkill Expwy and Center City digital at the top of range.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>4 - Content Engine</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>YouTube long-form + branded podcast</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Owned</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Compounding authority (Wakefield model).</t>
+      <c r="A14" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Detroit</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>4.3M</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>$1,200-$12,000</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>Detroit Free Press / The Detroit News</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>Crain's Detroit Business</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>I-75 / I-94 / M-10 corridors; International Outdoor runs 100+ Metro Detroit faces.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>4 - Content Engine</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>News-jacking / geo-triggered funnels</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Owned/Emerging</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Chloramine-switch play - already wired into n8n.</t>
+      <c r="A15" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>4.0M</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>$1,500-$14,000</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>The Seattle Times</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>Puget Sound Business Journal</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>Billboard supply constrained by regulation; I-5/I-405 corridors strongest.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>5 - Earned/PR</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>HARO + original water data as news</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>PR</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>Become the water expert reporters call. You have the data.</t>
+      <c r="A16" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Minneapolis</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>MN</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>3.7M</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>$1,200-$12,000</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>Star Tribune</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>Minneapolis/St. Paul Business Journal</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>Twin Cities; Franklin Outdoor runs 1,000+ illuminated boards across MN/W-WI.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>5 - Earned/PR</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Free water-testing events + lunch-and-learns</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Experiential</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Teach + test = pre-sold customers; B2B referral engine.</t>
+      <c r="A17" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>5.1M</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>$1,200-$10,000</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>The Arizona Republic</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Phoenix Business Journal</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>Freeway digital (Loop 101/202, I-10); sports-venue-adjacent units premium.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>6 - Frontier Edge</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>AEO / GEO (rank in AI answers)</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Emerging</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Almost no local competitor is doing this. Early-mover edge.</t>
+      <c r="A18" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Tampa</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>3.3M</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>$1,200-$11,000</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>Tampa Bay Times</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>Tampa Bay Business Journal</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>Tampa Bay (Hillsborough/Pinellas); I-4 / I-275 / Veterans Expwy corridors.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>6 - Frontier Edge</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>AI chatbot + voice booking agent</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Emerging/Other</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>24/7 capture of after-hours emergency leads. Your stack.</t>
+      <c r="A19" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>3.0M</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>$1,200-$11,000</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>The Denver Post</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Denver Business Journal</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>I-25 / I-70 corridors; Mile High Outdoor runs 400+ metro displays.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>6 - Frontier Edge</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>First-party CRM database</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Owned/Emerging</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>The asset that outlives every platform. Feed everything into it.</t>
+      <c r="A20" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Cleveland</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>2.2M</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>$1,000-$11,000</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>The Plain Dealer / cleveland.com</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>Crain's Cleveland Business</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>Cleveland/Akron/Canton; I-90 / I-77 / I-480 corridors; deep Ohio vendor stack.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Sacramento</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>2.4M</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>$1,200-$11,000</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>The Sacramento Bee</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>Sacramento Business Journal</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>Sacramento/Stockton/Modesto DMA; Clear Channel runs 1,280+ displays across 5 counties.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Orlando</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>2.8M</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>$1,200-$12,000</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>Orlando Sentinel</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>Orlando Business Journal</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>I-4 / theme-park &amp; tourist corridors carry premiums; strong visitor reach.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>St. Louis</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>2.8M</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>$1,000-$10,000</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>St. Louis Post-Dispatch</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>St. Louis Business Journal</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>Bi-state (MO/IL); DDI Media the dominant independent along I-70 and the Illinois side.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Pittsburgh</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>2.4M</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>$1,000-$9,000</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>Pittsburgh Post-Gazette</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>Pittsburgh Business Times</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="inlineStr">
+        <is>
+          <t>Parkway/tunnel approaches; strong independent scene (TM, Penneco, Steel City).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>3.3M</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>$1,500-$10,000</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>The San Diego Union-Tribune</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>San Diego Business Journal</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>I-5 / I-805 / I-15 / Hwy-78 corridors; limited inventory keeps rates firm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Baltimore</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>2.8M</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>$1,200-$11,000</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>The Baltimore Sun</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>Baltimore Business Journal</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr">
+        <is>
+          <t>I-95 / I-695 Beltway; Vision Outdoor is the Mid-Atlantic's independent digital operator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>2.8M</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>$1,000-$9,000</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>The Charlotte Observer</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Charlotte Business Journal</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>I-77 / I-85 / I-485 corridors; Adams Outdoor reaches 1.8M across 22 counties.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Raleigh</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>1.5M (Triangle ~2.1M)</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>$1,000-$10,000</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>The News &amp; Observer</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>Triangle Business Journal</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t>Research Triangle; I-40 / I-440 Beltline; Adams/Allison/Trailhead active regionally.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Indianapolis</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>2.1M</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>$1,000-$10,000</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>The Indianapolis Star</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>Indianapolis Business Journal</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>'Crossroads of America' — I-65/I-70/I-465; Lamar-dominant plus Keyes &amp; Reagan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Cincinnati</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>2.3M</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>$1,000-$10,000</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>The Cincinnati Enquirer</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>Cincinnati Business Courier</t>
+        </is>
+      </c>
+      <c r="J30" s="7" t="inlineStr">
+        <is>
+          <t>I-71 / I-75 / I-275 loop; tri-state (OH/KY/IN); Lamar &amp; Key-Ads strong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Las Vegas</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>2.3M</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>$1,500-$25,000</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>Las Vegas Review-Journal</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>Vegas Inc / LVRJ Business Press</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>The Strip commands outsized rates (spectaculars far higher); OUTFRONT reaches 99.9% weekly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>San Antonio</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>$1,000-$8,000</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>San Antonio Express-News</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>San Antonio Business Journal</t>
+        </is>
+      </c>
+      <c r="J32" s="7" t="inlineStr">
+        <is>
+          <t>I-10 / Loop 410 / US-281 the strongest placements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Portland</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>$1,200-$11,000</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>The Oregonian</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>Portland Business Journal</t>
+        </is>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>Lamar is the largest footprint + sole PDX operator; wallscapes in the Pearl/Downtown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Milwaukee</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>WI</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>1.6M</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>$1,000-$10,000</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>Milwaukee Journal Sentinel</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>Milwaukee Business Journal</t>
+        </is>
+      </c>
+      <c r="J34" s="7" t="inlineStr">
+        <is>
+          <t>I-94 / I-43 corridors; Lamar-dominant plus regional Ohio/Wisconsin operators.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Columbus</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>2.2M</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>$1,000-$9,000</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>The Columbus Dispatch</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>Columbus Business First</t>
+        </is>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>~2,200 boards; one of the Midwest's deepest OOH inventories (OAA of Ohio HQ'd here).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>Kansas City</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>2.2M</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>$1,000-$9,000</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>The Kansas City Star</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>Kansas City Business Journal</t>
+        </is>
+      </c>
+      <c r="J36" s="7" t="inlineStr">
+        <is>
+          <t>I-35/I-70; Ad-Trend the largest locally owned operator (since 1985).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Nashville</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>2.1M</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>$1,200-$11,000</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>The Tennessean</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>Nashville Business Journal</t>
+        </is>
+      </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>I-40 / I-24 / I-65 and Broadway/tourism demand; Allison Outdoor active regionally.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Salt Lake City</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>1.3M</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>$1,000-$9,000</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>The Salt Lake Tribune / Deseret News</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>Utah Business</t>
+        </is>
+      </c>
+      <c r="J38" s="7" t="inlineStr">
+        <is>
+          <t>I-15 corridor; Reagan Outdoor (HQ) &amp; YESCO dominate; billboards politically restricted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>New Orleans</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>1.3M</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>$1,000-$11,000</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>The Times-Picayune / NOLA.com / The Advocate</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>New Orleans CityBusiness</t>
+        </is>
+      </c>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>I-10 / French Quarter &amp; tourism demand; Lamar (Louisiana roots) &amp; Lindmark strong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Oklahoma City</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>$900-$8,000</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>The Oklahoman</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>The Journal Record</t>
+        </is>
+      </c>
+      <c r="J40" s="7" t="inlineStr">
+        <is>
+          <t>I-35 / I-40 / I-44; Lindmark, Headrick and BM cover Oklahoma broadly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Memphis</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>1.3M</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>$900-$8,000</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>The Commercial Appeal</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>Memphis Business Journal</t>
+        </is>
+      </c>
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>I-40 / I-55 freight corridors; Lamar-dominant plus Allison Outdoor regionally.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>1.3M</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>$900-$8,000</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>Richmond Times-Dispatch</t>
+        </is>
+      </c>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>Richmond BizSense</t>
+        </is>
+      </c>
+      <c r="J42" s="7" t="inlineStr">
+        <is>
+          <t>I-95 / I-64 corridors; Lamar &amp; OUTFRONT dominant in a supply-limited market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>$1,200-$12,000</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>Austin American-Statesman</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>Austin Business Journal</t>
+        </is>
+      </c>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>Reagan Outdoor-dominated; tech-driven demand along I-35 / MoPac / US-183.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Jacksonville</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>1.7M</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>$800-$6,000</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>The Florida Times-Union</t>
+        </is>
+      </c>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>Jacksonville Business Journal</t>
+        </is>
+      </c>
+      <c r="J44" s="7" t="inlineStr">
+        <is>
+          <t>Largest US city by land area; I-95 / I-295 corridors carry the value.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A2:J44"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:J1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H112"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>METRO OOH / BILLBOARD COMPANIES - 42 MARKETS</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Metros Served</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>HQ</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Pricing (availability)</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>AdQuick</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Broker / agency / marketplace</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>Nationwide (42 metros)</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr"/>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>https://www.adquick.com/</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Marketplace booking; publishes 2026 cost/CPM guides</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>AltTerrain</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Mobile / LED-truck operator</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>New York; Los Angeles; Chicago</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr"/>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>https://altterrain.com/</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>Mobile / street-level placements — quote only</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Billboard Connection</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Broker / agency / marketplace</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Nationwide (42 metros)</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>https://billboardconnection.com/</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Brokerage — designs, launches &amp; manages OOH campaigns</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>BillboardsIn</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Broker / agency / marketplace</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Nationwide (42 metros)</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr"/>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>https://www.billboardsin.com/</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Marketplace booking — dynamic</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Billups</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Broker / agency / marketplace</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Nationwide (42 metros)</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>https://www.billups.com/</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Managed-service buying across operators — quote only</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Blue Line Media</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Broker / agency / marketplace</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Nationwide (42 metros)</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr"/>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>https://www.bluelinemedia.com/</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>Brokerage; publishes market rate guides</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Branded Cities Network</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>National operator</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>New York; Los Angeles; Chicago</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr"/>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>https://www.brandedcities.com/</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Spectacular / landmark placements — quote only, high-end</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Brooklyn Outdoor</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>New York; Los Angeles; Chicago</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>https://brooklynoutdoor.com/</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Can't Miss US</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Mobile / LED-truck operator</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Nationwide (42 metros)</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr"/>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>https://cantmiss.us/</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Mobile digital billboard truck — quote only</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Capitol Outdoor</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>National operator</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Nationwide (8 metros)</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr"/>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>https://capitoloutdoor.com/</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Clear Channel Outdoor</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>National operator</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Nationwide (42 metros)</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>San Antonio, TX</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>https://clearchanneloutdoor.com/</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Digital Outdoor Advertising, LLC</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>National operator</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>New York; Washington DC; Boston; Philadelphia; Jacksonville</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr"/>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>https://digitaloutdooradvertising.com/</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Fliphound</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Broker / agency / marketplace</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Nationwide (42 metros)</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr"/>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>https://fliphound.com/</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>Self-serve; real-time pricing &amp; package rates</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Intersection</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>National operator</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>New York; Chicago; Philadelphia</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>https://www.intersection.com/</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>Digital kiosk / transit — quote only</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>JCDecaux</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>National operator</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>New York; Los Angeles; Chicago</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>https://www.jcdecaux.com/</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>Street furniture / airport / transit — quote only</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Lamar Advertising</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>National operator</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Nationwide (42 metros)</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>Baton Rouge, LA</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>https://lamar.com/</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>MediaLease OOH</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Broker / agency / marketplace</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Nationwide (42 metros)</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr"/>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>https://www.medialeaseooh.com/</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>New Tradition Media</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>National operator</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>New York; Los Angeles; Chicago; Portland</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>Chicago, IL</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>https://www.newtradition.com/</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>Premium / spectacular placements — quote only, high-end</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>OUTFRONT Media</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>National operator</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Nationwide (42 metros)</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>https://www.outfront.com/</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Van Wagner</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>National operator</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>New York; Los Angeles; Chicago</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>https://www.vanwagner.com/</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>Venue / sponsorship media — quote only</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Vector Media</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>National operator</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>New York; Chicago; Philadelphia</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>https://vectormedia.com/</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>Transit / experiential — quote only</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Becker Boards</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Chicago; San Francisco; Miami; Phoenix</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>https://www.beckerboards.com/</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Adams Outdoor Advertising</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>New York; Atlanta; Charlotte; Raleigh</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr"/>
+      <c r="F25" s="7" t="inlineStr"/>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Big Outdoor</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>Independent / local operator</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>New York; Philadelphia</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>https://bigoutdoor.com/</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>Digital spectacular — quote only</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Catalyst Outdoor Advertising</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>New York; Philadelphia</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr"/>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/catalyst-outdoor-advertising</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>Digital billboards — quote only</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Colossal Media</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>Independent / local operator</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>Brooklyn, NY</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>https://colossalmedia.com/</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>Hand-painted wallscape / mural — quote only</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>GSB Digital</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Independent / local operator</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>https://gsbdigital.com/</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>Wildposting / production — quote only</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Heritage Outdoor Media</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>Independent / local operator</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr"/>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>Times Square digital — quote only</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>InSite Street Media</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>https://www.insitestreetmedia.com/</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Neutron Media</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Independent / local operator</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr"/>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Pearl Media</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>https://pearlmedia.com/</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>Times Square / experiential — quote only</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>PMD Media</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr"/>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Red Rock Outdoor Advertising</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Independent / local operator</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr"/>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>Rolling Adz Mobile Billboards</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>Mobile / LED-truck operator</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>https://rollingadz.com/</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>Mobile billboard — day/route rate, quote only</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Seen Outdoor Media, LLC</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Independent / local operator</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>Brooklyn, NY</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr"/>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>SILVERCAST Media</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>Independent / local operator</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>https://www.silvercastmedia.com/</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>Oversized digital/static spectaculars — quote only, high-end</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>TSX Broadway (TSX Entertainment)</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>Independent / local operator</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr"/>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>Premium spectacular — quote only, very high-end</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Billboard Source</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>Broker / agency / marketplace</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Los Angeles; San Francisco</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr"/>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>https://www.billboardsource.com/billboard-advertising-in-san-francisco-ca</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Bray Outdoor Ads</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>Independent / local operator</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>Los Angeles; San Diego</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr"/>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>https://brayoutdoor.com/</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Bulletin Displays</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>https://www.bulletindisplays.com/</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>O Media Group</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>Independent / local operator</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr"/>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Regency Outdoor Advertising</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>West Hollywood, CA</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>https://regencyoutdoor.com/</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>Premium bulletins/spectaculars — quote only, high-end</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>GreenSigns Chicago</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>Independent / local operator</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>Chicago, IL</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr"/>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>Digital billboard — quote only</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Image Media Outdoor</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>Chicago, IL</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>https://imageoutdoor.com/</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>J&amp;B Signs Inc</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>Independent / local operator</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>Chicago, IL</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr"/>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>Outdoor Impact</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>Independent / local operator</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>Chicago, IL</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>https://www.outdoorimpact.com/</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Red Star Outdoor</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>Chicago, IL</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr"/>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>VC Outdoor</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>Independent / local operator</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>Chicago, IL</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr"/>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>Wildposting / wallscape / bus wrap — quote only</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>True Impact Media</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>Broker / agency / marketplace</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>San Francisco; San Antonio</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr"/>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>https://trueimpactmedia.com/billboard-advertising-in-san-antonio/</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>Billboards + mobile — quote only</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>Billboard Company Atlanta</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>Independent / local operator</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>https://billboardcompanyatlanta.com/</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>Trailhead Media</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>Atlanta; Charlotte; Raleigh</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr"/>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>https://trailheadmedia.com/</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>Digital Outdoor Advertising — DC</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>Washington DC</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr"/>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>https://digitaloutdooradvertising.com/</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>Albert Outdoor Advertising</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>Independent / local operator</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr"/>
+      <c r="F55" s="7" t="inlineStr"/>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>Arrington Outdoor Advertising</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>Dallas, TX</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>https://www.arringtonoutdoor.com/</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>Billboards America</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>Broker / agency / marketplace</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>Dallas; Houston; San Antonio</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr"/>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>https://www.billboardsamerica.com/billboard-advertising-locations/texas</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>BM Outdoor Media</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>Nationwide (19 metros)</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr"/>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>https://bmoutdoor.com/</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>Dallas Billboards LLC</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>Broker / agency / marketplace</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>Dallas, TX</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>https://www.dallasbillboards.com/</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>Media buyer / creative agency — quote only</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>Lux Media</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>Mobile / LED-truck operator</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>Dallas; Houston; San Antonio; Austin</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr"/>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>https://www.luxmediaads.com/</t>
+        </is>
+      </c>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>Mobile LED truck — day/route rate, quote only</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>Premier Mobile Billboards</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>Mobile / LED-truck operator</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>Dallas; Houston; San Antonio</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>Houston, TX</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>https://premiermobilebillboards.com/</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>Mobile LED truck — quote only</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>Ralston Outdoor Advertising</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr"/>
+      <c r="F62" s="7" t="inlineStr"/>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>SignAd Outdoor Advertising</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>Dallas; Houston; San Antonio</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>Houston, TX</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>https://www.signad.com/</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>Avail Media Group</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>Broker / agency / marketplace</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>Houston, TX</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>https://www.availmediagroup.com/capabilities/out-of-home</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>Independent agency — negotiates across vendors</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>Gilbreath Outdoor Advertising</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>Houston; San Antonio</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>Houston, TX</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>https://www.gilbreathoutdoor.com/</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>Inspiria Outdoor Advertising</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>Independent / local operator</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>Houston, TX</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>https://inspiriaoutdoor.com/houston-advertising/</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>MH Outdoor Media</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>Independent / local operator</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>Houston, TX</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr"/>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>Carter Outdoor Advertising</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>Miami</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr"/>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>https://www.carteroutdoor.com/</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>Plug Talk Media</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>Broker / agency / marketplace</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>Miami</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr"/>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>https://www.plugtalk.media/our-markets/miami</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>Programmatic/DOOH — dynamic</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>SDE Media</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>Independent / local operator</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>Miami</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>Miami, FL</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>https://sde-media.com/</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>Keystone Outdoor Advertising</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr"/>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>https://www.keystoneoutdoor.com/</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>International Outdoor</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>Detroit</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>Detroit, MI</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>https://iobillboard.com/</t>
+        </is>
+      </c>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>Pacific Outdoor Advertising</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>Independent / local operator</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr"/>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>https://www.pacificoutdooradvertising.com/</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>Parker Outdoor Inc.</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>Independent / local operator</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr"/>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>https://www.parkeroutdoorinc.com/billboards/western-washington/seattle</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H74" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>Summus Outdoor</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr"/>
+      <c r="F75" s="7" t="inlineStr"/>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H75" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>Blue Ox Media</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>Independent / local operator</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>Minneapolis</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>https://www.blueoxmediagroup.com/</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>Digital billboard — quote only</t>
+        </is>
+      </c>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>Franklin Outdoor Advertising</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>Minneapolis</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr"/>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>https://franklinoutdoor.com/</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>American Outdoor Advertising</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>Independent / local operator</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>Phoenix; San Diego</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr"/>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>https://www.americanoutdoor.com/</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>Arizona Billboard Company</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>Independent / local operator</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>https://arizonabillboardcompany.com/</t>
+        </is>
+      </c>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>Logan Outdoor Advertising</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>Tampa</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr"/>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>https://loganoutdoor.com/</t>
+        </is>
+      </c>
+      <c r="G80" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>Signal Outdoor Advertising</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>Tampa</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr"/>
+      <c r="F81" s="7" t="inlineStr"/>
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>Tampa Outdoor Advertising</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>Tampa</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>Tampa, FL</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>https://tampaoutdoor.com/</t>
+        </is>
+      </c>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>Elevation Outdoor Advertising</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr"/>
+      <c r="F83" s="7" t="inlineStr"/>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H83" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>Mile High Outdoor</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>Denver, CO</t>
+        </is>
+      </c>
+      <c r="F84" s="7" t="inlineStr">
+        <is>
+          <t>https://milehighoutdoor.com/</t>
+        </is>
+      </c>
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H84" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>Outdoor Ads, Inc.</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>Independent / local operator</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>Denver, CO</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr"/>
+      <c r="G85" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H85" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>American Outdoor Advertising (Columbus)</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>Cleveland; Cincinnati; Columbus</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>Columbus, OH</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>http://www.americanoutdooradvertising.net/</t>
+        </is>
+      </c>
+      <c r="G86" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H86" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>Key-Ads, Inc.</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>Cleveland; Cincinnati; Columbus</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr"/>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>https://www.key-ads.com/</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H87" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>Outdoor Advertising Center</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>Cleveland; Cincinnati; Milwaukee; Columbus</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr"/>
+      <c r="F88" s="7" t="inlineStr">
+        <is>
+          <t>https://www.outdooradvertisingcenter.com/</t>
+        </is>
+      </c>
+      <c r="G88" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H88" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>Orlando Outdoor</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>Orlando</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>Orlando, FL</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>https://www.orlandooutdoor.com/</t>
+        </is>
+      </c>
+      <c r="G89" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H89" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>DDI Media</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>St. Louis</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr"/>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>https://www.ddimedia.net/our-markets/missouri/st-louis-area</t>
+        </is>
+      </c>
+      <c r="G90" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H90" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>Robinson Outdoor</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>Independent / local operator</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>St. Louis</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr"/>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>https://robinsonoutdoorllc.com/locations/st-louis-imperial/</t>
+        </is>
+      </c>
+      <c r="G91" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H91" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>Penneco Outdoor Advertising</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>Pittsburgh</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="inlineStr"/>
+      <c r="F92" s="7" t="inlineStr">
+        <is>
+          <t>https://pennecooutdoor.com/</t>
+        </is>
+      </c>
+      <c r="G92" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H92" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>Steel City Billboards</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>Independent / local operator</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>Pittsburgh</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA</t>
+        </is>
+      </c>
+      <c r="F93" s="7" t="inlineStr">
+        <is>
+          <t>https://steelcitybillboards.com/</t>
+        </is>
+      </c>
+      <c r="G93" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H93" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>TM Advertising</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>Pittsburgh</t>
+        </is>
+      </c>
+      <c r="E94" s="7" t="inlineStr"/>
+      <c r="F94" s="7" t="inlineStr">
+        <is>
+          <t>https://tmbillboard.com/</t>
+        </is>
+      </c>
+      <c r="G94" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H94" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>Vision Outdoor</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>Pittsburgh; Baltimore</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>Baltimore, MD</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>https://visionoutdoormd.com/</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H95" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t>Allison Outdoor Advertising</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>Charlotte; Raleigh; Nashville; Memphis</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr"/>
+      <c r="F96" s="7" t="inlineStr">
+        <is>
+          <t>https://www.allisonoutdoor.com/</t>
+        </is>
+      </c>
+      <c r="G96" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H96" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>Keyes Outdoor Advertising</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>Independent / local operator</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>Indianapolis</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>http://www.keyesoutdoor.com/</t>
+        </is>
+      </c>
+      <c r="G97" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H97" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" s="7" t="inlineStr">
+        <is>
+          <t>Reagan Outdoor Advertising</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>Indianapolis; Las Vegas; Salt Lake City; Austin</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT</t>
+        </is>
+      </c>
+      <c r="F98" s="7" t="inlineStr">
+        <is>
+          <t>https://www.reaganoutdoor.com/</t>
+        </is>
+      </c>
+      <c r="G98" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H98" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" s="7" t="inlineStr">
+        <is>
+          <t>Las Vegas Billboards</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>Independent / local operator</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>Las Vegas</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>https://lasvegasbillboards.com/</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr">
+        <is>
+          <t>Strip placements premium — quote only</t>
+        </is>
+      </c>
+      <c r="H99" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>Grapevine Outdoor</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>Portland</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>Portland, OR</t>
+        </is>
+      </c>
+      <c r="F100" s="7" t="inlineStr">
+        <is>
+          <t>https://grapevineoutdoor.com/</t>
+        </is>
+      </c>
+      <c r="G100" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H100" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>Meadow Outdoor Advertising</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>Portland</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="inlineStr"/>
+      <c r="F101" s="7" t="inlineStr"/>
+      <c r="G101" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H101" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" s="7" t="inlineStr">
+        <is>
+          <t>Kenjoh Outdoor</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="inlineStr">
+        <is>
+          <t>Independent / local operator</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>Columbus</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="inlineStr"/>
+      <c r="F102" s="7" t="inlineStr"/>
+      <c r="G102" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H102" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" s="7" t="inlineStr">
+        <is>
+          <t>Ad-Trend</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>Kansas City</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>Kansas City, MO</t>
+        </is>
+      </c>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
+          <t>http://www.ad-trend.com/</t>
+        </is>
+      </c>
+      <c r="G103" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H103" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>Midwest Billboards</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>Kansas City</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="inlineStr"/>
+      <c r="F104" s="7" t="inlineStr">
+        <is>
+          <t>https://midwestbillboards.com/</t>
+        </is>
+      </c>
+      <c r="G104" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H104" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>YESCO Outdoor Media</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>Salt Lake City</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT</t>
+        </is>
+      </c>
+      <c r="F105" s="7" t="inlineStr">
+        <is>
+          <t>https://www.yesco.com/saltlakecity/outdoor-advertising/</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H105" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>Lindmark Outdoor Media</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>New Orleans; Oklahoma City</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="inlineStr"/>
+      <c r="F106" s="7" t="inlineStr"/>
+      <c r="G106" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H106" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>Headrick Outdoor Media</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="inlineStr">
+        <is>
+          <t>Regional operator</t>
+        </is>
+      </c>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>Oklahoma City</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="inlineStr"/>
+      <c r="F107" s="7" t="inlineStr">
+        <is>
+          <t>https://www.headrickoutdoormedia.com/</t>
+        </is>
+      </c>
+      <c r="G107" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H107" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>Burkett Media</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t>Independent / local operator</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="inlineStr"/>
+      <c r="F108" s="7" t="inlineStr"/>
+      <c r="G108" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H108" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="6" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>MediaChoice</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="inlineStr">
+        <is>
+          <t>Independent / local operator</t>
+        </is>
+      </c>
+      <c r="D109" s="7" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="E109" s="7" t="inlineStr"/>
+      <c r="F109" s="7" t="inlineStr"/>
+      <c r="G109" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H109" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" s="7" t="inlineStr">
+        <is>
+          <t>American Mobile Ads</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="inlineStr">
+        <is>
+          <t>Mobile / LED-truck operator</t>
+        </is>
+      </c>
+      <c r="D110" s="7" t="inlineStr">
+        <is>
+          <t>Jacksonville</t>
+        </is>
+      </c>
+      <c r="E110" s="7" t="inlineStr"/>
+      <c r="F110" s="7" t="inlineStr">
+        <is>
+          <t>https://americanmobileads.com/markets/jacksonville</t>
+        </is>
+      </c>
+      <c r="G110" s="7" t="inlineStr">
+        <is>
+          <t>Mobile LED truck — day/route rate, quote only</t>
+        </is>
+      </c>
+      <c r="H110" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="6" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" s="7" t="inlineStr">
+        <is>
+          <t>Daily Billboards</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="inlineStr">
+        <is>
+          <t>Independent / local operator</t>
+        </is>
+      </c>
+      <c r="D111" s="7" t="inlineStr">
+        <is>
+          <t>Jacksonville</t>
+        </is>
+      </c>
+      <c r="E111" s="7" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL</t>
+        </is>
+      </c>
+      <c r="F111" s="7" t="inlineStr"/>
+      <c r="G111" s="7" t="inlineStr">
+        <is>
+          <t>Static ~$1k–$25k+/4wk; premium/spectacular boards much higher (market avg)</t>
+        </is>
+      </c>
+      <c r="H111" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" s="7" t="inlineStr">
+        <is>
+          <t>Fisher Design &amp; Advertising</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="inlineStr">
+        <is>
+          <t>Broker / agency / marketplace</t>
+        </is>
+      </c>
+      <c r="D112" s="7" t="inlineStr">
+        <is>
+          <t>Jacksonville</t>
+        </is>
+      </c>
+      <c r="E112" s="7" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL</t>
+        </is>
+      </c>
+      <c r="F112" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fisherdesignandadvertising.com/services/outdoor-advertising-jacksonville/</t>
+        </is>
+      </c>
+      <c r="G112" s="7" t="inlineStr">
+        <is>
+          <t>Agency — books across outdoor vendors, quote only</t>
+        </is>
+      </c>
+      <c r="H112" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:H112"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -58104,6 +63883,457 @@
   <autoFilter ref="A2:F141"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>B. SYMBOLIC — PALM BEACH COUNTY PRIORITY PLAYBOOK</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Why it wins for you</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>1 - Foundation</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Google Business Profile + Reviews</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Search/Local</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>FREE, drives the map pack. Non-negotiable base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>1 - Foundation</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Google Local Service Ads (LSA)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Search/Local</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Best trades lead quality; you're license/insurance-qualified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>1 - Foundation</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>CallRail call tracking</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Tools</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Attribute every call to the campaign that drove it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>2 - Relationships</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Property manager / HOA agreements</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Partnership</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Recurring commercial - highest LTV in PBC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>2 - Relationships</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Realtor + home-inspector + restoration referrals</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Partnership</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Renewable, pre-qualified lead sources for free.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>2 - Relationships</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Water-filtration certified-installer status</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Partnership</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Qualified inbound + co-marketing on your water side.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>3 - Local Saturation</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Vehicle wraps + yard signs + door hangers</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Local/OOH</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Cheap saturation in your exact service area. Produce in-house.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>3 - Local Saturation</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Fridge/emergency magnets + shutoff-valve tags</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Promo</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Year-round visibility; shutoff tags are a unique differentiator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>3 - Local Saturation</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Nextdoor + Facebook local Groups</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Trust-based, near-free, converts like referrals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>4 - Content Engine</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>City landing pages + Local SEO</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Owned</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>One page per PBC city, each in its own map pack.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>4 - Content Engine</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Interactive tools (Hard Water Map, calculators, quiz)</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Owned</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>You already build these; gate them, feed the CRM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>4 - Content Engine</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>YouTube long-form + branded podcast</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Owned</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Compounding authority (Wakefield model).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>4 - Content Engine</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>News-jacking / geo-triggered funnels</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Owned/Emerging</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Chloramine-switch play - already wired into n8n.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>5 - Earned/PR</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>HARO + original water data as news</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Become the water expert reporters call. You have the data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>5 - Earned/PR</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Free water-testing events + lunch-and-learns</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Experiential</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Teach + test = pre-sold customers; B2B referral engine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>6 - Frontier Edge</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>AEO / GEO (rank in AI answers)</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Emerging</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Almost no local competitor is doing this. Early-mover edge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>6 - Frontier Edge</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>AI chatbot + voice booking agent</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Emerging/Other</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>24/7 capture of after-hours emergency leads. Your stack.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>6 - Frontier Edge</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>First-party CRM database</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Owned/Emerging</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>The asset that outlives every platform. Feed everything into it.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/marketing-repository/data/BSymbolic_Marketing_Master_Expanded.xlsx
+++ b/marketing-repository/data/BSymbolic_Marketing_Master_Expanded.xlsx
@@ -36,7 +36,8 @@
     <sheet name="Cause and Community" sheetId="27" state="visible" r:id="rId27"/>
     <sheet name="US Metro Reference" sheetId="28" state="visible" r:id="rId28"/>
     <sheet name="Metro OOH Companies" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="PBC Priority Playbook" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Quick-Start by Metro" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="PBC Priority Playbook" sheetId="31" state="visible" r:id="rId31"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master List'!$A$2:$G$1118</definedName>
@@ -65,8 +66,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'Branding and Creative'!$A$2:$F$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'B2B and Account-Based'!$A$2:$F$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'Cause and Community'!$A$2:$F$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'US Metro Reference'!$A$2:$J$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'US Metro Reference'!$A$2:$M$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'Metro OOH Companies'!$A$2:$H$112</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="29" hidden="1">'Quick-Start by Metro'!$A$2:$I$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -75,7 +77,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -94,6 +96,10 @@
     <font>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
     </font>
   </fonts>
   <fills count="7">
@@ -155,7 +161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -182,6 +188,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -671,7 +680,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>US Metro Reference = 42 largest markets with DMA rank, population, OOH rate band, # billboard operators, dominant newspaper &amp; business journal. Metro OOH Companies = 110 scraped billboard/OOH operators by metro. Turns the tactic menu into a US market reference.</t>
+          <t>US Metro Reference = 42 largest markets with DMA rank, population, OOH rate band, # billboard operators, newspaper, business journal, Big-4 TV affiliates, major radio groups &amp; notable ad agencies. Metro OOH Companies = 110 scraped billboard/OOH operators by metro. Quick-Start by Metro = who to call in each market (top local OOH operators, TV/radio/paper, agencies) + the universal foundation steps. TV/radio/agency data is reference-level - verify before buying.</t>
         </is>
       </c>
     </row>
@@ -53836,7 +53845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -53846,9 +53855,12 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="55" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="36" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
+    <col width="48" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -53866,6 +53878,9 @@
       <c r="H1" s="2" t="n"/>
       <c r="I1" s="2" t="n"/>
       <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -53914,6 +53929,21 @@
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Big-4 TV Affiliates</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Major Radio Groups</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Notable Ad Agencies</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
         <is>
           <t>Market Notes</t>
         </is>
@@ -53961,6 +53991,21 @@
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
+          <t>WABC 7 · WCBS 2 · WNBC 4 · WNYW Fox 5</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>Audacy (WFAN, 1010 WINS) · iHeart (Z100) · SBS (Spanish, HQ)</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>Ogilvy, BBDO, Droga5, McCann (global HQs)</t>
+        </is>
+      </c>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
           <t>Times Square spectaculars $10,000 to $1,000,000+/mo; Manhattan digital $15k–$50k; outer-borough static $3k–$8k.</t>
         </is>
       </c>
@@ -54007,6 +54052,21 @@
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
+          <t>KABC 7 · KCBS 2 · KNBC 4 · KTTV Fox 11</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="inlineStr">
+        <is>
+          <t>iHeart (KIIS, KFI) · Audacy (KROQ, KNX) · Univision/SBS (Spanish)</t>
+        </is>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>Deutsch LA, 72andSunny, TBWA\Chiat\Day</t>
+        </is>
+      </c>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
           <t>Iconic Sunset Strip bulletins command a large multiple of comparable units 30 mi east.</t>
         </is>
       </c>
@@ -54053,6 +54113,21 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
+          <t>WLS 7 · WBBM 2 · WMAQ 5 · WFLD Fox 32</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>Audacy (WBBM, WSCR) · iHeart · Nexstar (WGN Radio)</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>Leo Burnett, FCB Chicago, Energy BBDO</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
           <t>Premium expressway (Kennedy/Dan Ryan) and Loop digital displays at the high end.</t>
         </is>
       </c>
@@ -54099,6 +54174,21 @@
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
+          <t>KGO 7 · KPIX 5 · KNTV 11 · KTVU Fox 2</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>Audacy (KCBS) · iHeart · Bonneville</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>Goodby Silverstein, Duncan Channon, Argonaut</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
           <t>Bay Area (SF/Oakland/San Jose); tech-driven demand and scarce inventory keep rates high.</t>
         </is>
       </c>
@@ -54145,6 +54235,21 @@
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
+          <t>WSB 2 · WANF 46 · WXIA 11 · WAGA Fox 5</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>Cox Media Group (HQ, WSB) · iHeart · Urban One</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>22squared, Dagger, Chemistry</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
           <t>Connector/I-285 'Perimeter' corridors; large billboard-friendly metro.</t>
         </is>
       </c>
@@ -54191,6 +54296,21 @@
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
+          <t>WJLA 7 · WUSA 9 · WRC 4 · WTTG Fox 5</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>Hubbard (WTOP — top-billing US station) · iHeart · Cumulus (WMAL)</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>GMMB (political), RP3 Agency</t>
+        </is>
+      </c>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
           <t>Billboards tightly limited in DC proper; value concentrated on MD/VA approaches &amp; transit.</t>
         </is>
       </c>
@@ -54237,6 +54357,21 @@
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
+          <t>WCVB 5 · WBZ 4 · WBTS 10 · WFXT Fox 25</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>iHeart (WBZ-AM) · Audacy (WEEI) · Beasley</t>
+        </is>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>Hill Holliday, Arnold, MullenLowe, Allen &amp; Gerritsen</t>
+        </is>
+      </c>
+      <c r="M9" s="7" t="inlineStr">
+        <is>
           <t>OUTFRONT #1 with 675+ digital faces; I-93/Mass Pike and tunnel approaches priced highest.</t>
         </is>
       </c>
@@ -54283,6 +54418,21 @@
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
+          <t>WFAA 8 · KTVT 11 · KXAS 5 · KDFW Fox 4</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>iHeart · Audacy (KRLD) · Cumulus (WBAP)</t>
+        </is>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>TRG (The Richards Group), Dieste (Hispanic)</t>
+        </is>
+      </c>
+      <c r="M10" s="7" t="inlineStr">
+        <is>
           <t>High-traffic corridors (I-35, LBJ, Central Expwy) priced highest.</t>
         </is>
       </c>
@@ -54329,6 +54479,21 @@
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
+          <t>KTRK 13 · KHOU 11 · KPRC 2 · KRIV Fox 26</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>iHeart (KTRH) · Audacy · Cox (KKBQ)</t>
+        </is>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>Lopez Negrete (Hispanic), MMI Agency</t>
+        </is>
+      </c>
+      <c r="M11" s="7" t="inlineStr">
+        <is>
           <t>Clear Channel alone runs 2,000+ boards across 13 counties (99% of DMA adults).</t>
         </is>
       </c>
@@ -54375,6 +54540,21 @@
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
+          <t>WPLG 10 · WFOR 4 · WTVJ 6 · WSVN Fox 7</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>iHeart · Cox · SBS (Spanish broadcasting HQ)</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>Zimmerman, Crispin (legacy), República Havas (Hispanic)</t>
+        </is>
+      </c>
+      <c r="M12" s="7" t="inlineStr">
+        <is>
           <t>I-95 / Palmetto / Dolphin Expwy and beach/tourism corridors carry premiums.</t>
         </is>
       </c>
@@ -54421,6 +54601,21 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
+          <t>WPVI 6 · KYW 3 · WCAU 10 · WTXF Fox 29</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>Audacy (HQ — KYW, WIP) · iHeart · Beasley (WMMR)</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>Digitas Philly (legacy), Brownstein Group, LevLane</t>
+        </is>
+      </c>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
           <t>I-95 / Schuylkill Expwy and Center City digital at the top of range.</t>
         </is>
       </c>
@@ -54467,6 +54662,21 @@
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
+          <t>WXYZ 7 · WWJ 62 · WDIV 4 · WJBK Fox 2</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>Audacy (WWJ, WXYT) · iHeart · Cumulus (WJR)</t>
+        </is>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>Doner, Campbell Ewald, Lafayette American</t>
+        </is>
+      </c>
+      <c r="M14" s="7" t="inlineStr">
+        <is>
           <t>I-75 / I-94 / M-10 corridors; International Outdoor runs 100+ Metro Detroit faces.</t>
         </is>
       </c>
@@ -54513,6 +54723,21 @@
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
+          <t>KOMO 4 · KIRO 7 · KING 5 · KCPQ Fox 13</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>Bonneville (KIRO) · iHeart · Audacy</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>Wongdoody, Copacino Fujikado, DNA</t>
+        </is>
+      </c>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
           <t>Billboard supply constrained by regulation; I-5/I-405 corridors strongest.</t>
         </is>
       </c>
@@ -54559,6 +54784,21 @@
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
+          <t>KSTP 5 · WCCO 4 · KARE 11 · KMSP Fox 9</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>Hubbard (HQ — KSTP, KS95) · iHeart (KFAN) · Audacy (WCCO)</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>Fallon, Colle McVoy, Periscope</t>
+        </is>
+      </c>
+      <c r="M16" s="7" t="inlineStr">
+        <is>
           <t>Twin Cities; Franklin Outdoor runs 1,000+ illuminated boards across MN/W-WI.</t>
         </is>
       </c>
@@ -54605,6 +54845,21 @@
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
+          <t>KNXV 15 · KPHO 5 · KPNX 12 · KSAZ Fox 10</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>Bonneville (KTAR) · iHeart · Hubbard</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>OH Partners, LaneTerralever, Zion &amp; Zion</t>
+        </is>
+      </c>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
           <t>Freeway digital (Loop 101/202, I-10); sports-venue-adjacent units premium.</t>
         </is>
       </c>
@@ -54651,6 +54906,21 @@
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
+          <t>WFTS 28 · WTSP 10 · WFLA 8 · WTVT Fox 13</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>iHeart (WFLA-AM) · Cox · Beasley (WQYK)</t>
+        </is>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>PPK, Schifino Lee</t>
+        </is>
+      </c>
+      <c r="M18" s="7" t="inlineStr">
+        <is>
           <t>Tampa Bay (Hillsborough/Pinellas); I-4 / I-275 / Veterans Expwy corridors.</t>
         </is>
       </c>
@@ -54697,6 +54967,21 @@
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
+          <t>KMGH 7 · KCNC 4 · KUSA 9 · KDVR Fox 31</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>iHeart (KOA) · Bonneville (KYGO/KOSI) · Audacy</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>Karsh Hagan, Cactus, Grit Advertising</t>
+        </is>
+      </c>
+      <c r="M19" s="7" t="inlineStr">
+        <is>
           <t>I-25 / I-70 corridors; Mile High Outdoor runs 400+ metro displays.</t>
         </is>
       </c>
@@ -54743,6 +55028,21 @@
       </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
+          <t>WEWS 5 · WOIO 19 · WKYC 3 · WJW Fox 8</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>iHeart (WTAM) · Audacy · Good Karma (WKNR)</t>
+        </is>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>Marcus Thomas, Adcom, Falls</t>
+        </is>
+      </c>
+      <c r="M20" s="7" t="inlineStr">
+        <is>
           <t>Cleveland/Akron/Canton; I-90 / I-77 / I-480 corridors; deep Ohio vendor stack.</t>
         </is>
       </c>
@@ -54789,6 +55089,21 @@
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
+          <t>KXTV 10 · KOVR 13 · KCRA 3 · KTXL Fox 40</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>iHeart (KFBK) · Audacy · Bonneville</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>The Glass Agency, Position Interactive</t>
+        </is>
+      </c>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
           <t>Sacramento/Stockton/Modesto DMA; Clear Channel runs 1,280+ displays across 5 counties.</t>
         </is>
       </c>
@@ -54835,6 +55150,21 @@
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
+          <t>WFTV 9 · WKMG 6 · WESH 2 · WOFL Fox 35</t>
+        </is>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t>iHeart · Cox (WDBO)</t>
+        </is>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>&amp;Barr, PUSH</t>
+        </is>
+      </c>
+      <c r="M22" s="7" t="inlineStr">
+        <is>
           <t>I-4 / theme-park &amp; tourist corridors carry premiums; strong visitor reach.</t>
         </is>
       </c>
@@ -54881,6 +55211,21 @@
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
+          <t>KDNL 30 · KMOV 4 · KSDK 5 · KTVI Fox 2</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>Audacy (KMOX) · iHeart · Hubbard</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>HLK, Rodgers Townsend (DDB)</t>
+        </is>
+      </c>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
           <t>Bi-state (MO/IL); DDI Media the dominant independent along I-70 and the Illinois side.</t>
         </is>
       </c>
@@ -54927,6 +55272,21 @@
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
+          <t>WTAE 4 · KDKA 2 · WPXI 11 · WPGH Fox 53</t>
+        </is>
+      </c>
+      <c r="K24" s="7" t="inlineStr">
+        <is>
+          <t>Audacy (KDKA) · iHeart (WDVE) · Steel City Media</t>
+        </is>
+      </c>
+      <c r="L24" s="7" t="inlineStr">
+        <is>
+          <t>Brunner, MARC USA (legacy), Gatesman</t>
+        </is>
+      </c>
+      <c r="M24" s="7" t="inlineStr">
+        <is>
           <t>Parkway/tunnel approaches; strong independent scene (TM, Penneco, Steel City).</t>
         </is>
       </c>
@@ -54973,6 +55333,21 @@
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
+          <t>KGTV 10 · KFMB 8 · KNSD 7/39 · KSWB Fox 5</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>iHeart (KOGO) · Audacy · Local Media San Diego</t>
+        </is>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>VITRO (Petco work), i.d.e.a.</t>
+        </is>
+      </c>
+      <c r="M25" s="7" t="inlineStr">
+        <is>
           <t>I-5 / I-805 / I-15 / Hwy-78 corridors; limited inventory keeps rates firm.</t>
         </is>
       </c>
@@ -55019,6 +55394,21 @@
       </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
+          <t>WMAR 2 · WJZ 13 · WBAL 11 · WBFF Fox 45</t>
+        </is>
+      </c>
+      <c r="K26" s="7" t="inlineStr">
+        <is>
+          <t>Hearst (WBAL radio) · iHeart · Audacy</t>
+        </is>
+      </c>
+      <c r="L26" s="7" t="inlineStr">
+        <is>
+          <t>Planit, GKV, idfive</t>
+        </is>
+      </c>
+      <c r="M26" s="7" t="inlineStr">
+        <is>
           <t>I-95 / I-695 Beltway; Vision Outdoor is the Mid-Atlantic's independent digital operator.</t>
         </is>
       </c>
@@ -55065,6 +55455,21 @@
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
+          <t>WSOC 9 · WBTV 3 · WCNC 36 · WJZY Fox 46</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>iHeart · Urban One · Norsan Media (Spanish, local)</t>
+        </is>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>Wray Ward, Luquire</t>
+        </is>
+      </c>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
           <t>I-77 / I-85 / I-485 corridors; Adams Outdoor reaches 1.8M across 22 counties.</t>
         </is>
       </c>
@@ -55111,6 +55516,21 @@
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
+          <t>WTVD 11 · WNCN 17 · WRAL 5 · WRAZ Fox 50</t>
+        </is>
+      </c>
+      <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t>iHeart · Curtis Media (local Triangle) · Capitol Broadcasting</t>
+        </is>
+      </c>
+      <c r="L28" s="7" t="inlineStr">
+        <is>
+          <t>McKinney (Durham), Baldwin&amp;</t>
+        </is>
+      </c>
+      <c r="M28" s="7" t="inlineStr">
+        <is>
           <t>Research Triangle; I-40 / I-440 Beltline; Adams/Allison/Trailhead active regionally.</t>
         </is>
       </c>
@@ -55157,6 +55577,21 @@
       </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
+          <t>WRTV 6 · WTTV 4 · WTHR 13 · WXIN Fox 59</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>iHeart · Cumulus (WFMS) · Urban One</t>
+        </is>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>Young &amp; Laramore, Hirons</t>
+        </is>
+      </c>
+      <c r="M29" s="7" t="inlineStr">
+        <is>
           <t>'Crossroads of America' — I-65/I-70/I-465; Lamar-dominant plus Keyes &amp; Reagan.</t>
         </is>
       </c>
@@ -55203,6 +55638,21 @@
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
+          <t>WCPO 9 · WKRC 12 · WLWT 5 · WXIX Fox 19</t>
+        </is>
+      </c>
+      <c r="K30" s="7" t="inlineStr">
+        <is>
+          <t>iHeart (700WLW) · Hubbard (WKRQ) · Cumulus</t>
+        </is>
+      </c>
+      <c r="L30" s="7" t="inlineStr">
+        <is>
+          <t>Curiosity, Barefoot Proximity (BBDO)</t>
+        </is>
+      </c>
+      <c r="M30" s="7" t="inlineStr">
+        <is>
           <t>I-71 / I-75 / I-275 loop; tri-state (OH/KY/IN); Lamar &amp; Key-Ads strong.</t>
         </is>
       </c>
@@ -55249,6 +55699,21 @@
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
+          <t>KTNV 13 · KLAS 8 · KSNV 3 · KVVU Fox 5</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>Audacy · iHeart · Lotus (local)</t>
+        </is>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>R&amp;R Partners ('What happens here, stays here')</t>
+        </is>
+      </c>
+      <c r="M31" s="7" t="inlineStr">
+        <is>
           <t>The Strip commands outsized rates (spectaculars far higher); OUTFRONT reaches 99.9% weekly.</t>
         </is>
       </c>
@@ -55295,6 +55760,21 @@
       </c>
       <c r="J32" s="7" t="inlineStr">
         <is>
+          <t>KSAT 12 · KENS 5 · WOAI 4 · KABB Fox 29</t>
+        </is>
+      </c>
+      <c r="K32" s="7" t="inlineStr">
+        <is>
+          <t>iHeartMedia (corporate HQ — WOAI) · Cox · Univision (Spanish)</t>
+        </is>
+      </c>
+      <c r="L32" s="7" t="inlineStr">
+        <is>
+          <t>The Atkins Group, Giles-Parscale (legacy)</t>
+        </is>
+      </c>
+      <c r="M32" s="7" t="inlineStr">
+        <is>
           <t>I-10 / Loop 410 / US-281 the strongest placements.</t>
         </is>
       </c>
@@ -55341,6 +55821,21 @@
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
+          <t>KATU 2 · KOIN 6 · KGW 8 · KPTV Fox 12</t>
+        </is>
+      </c>
+      <c r="K33" s="7" t="inlineStr">
+        <is>
+          <t>iHeart (KEX) · Audacy · Alpha Media (HQ Portland)</t>
+        </is>
+      </c>
+      <c r="L33" s="7" t="inlineStr">
+        <is>
+          <t>Wieden+Kennedy (HQ), Instrument, Opinionated</t>
+        </is>
+      </c>
+      <c r="M33" s="7" t="inlineStr">
+        <is>
           <t>Lamar is the largest footprint + sole PDX operator; wallscapes in the Pearl/Downtown.</t>
         </is>
       </c>
@@ -55387,6 +55882,21 @@
       </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
+          <t>WISN 12 · WDJT 58 · WTMJ 4 · WITI Fox 6</t>
+        </is>
+      </c>
+      <c r="K34" s="7" t="inlineStr">
+        <is>
+          <t>Good Karma (WTMJ radio) · iHeart · Saga (WKLH)</t>
+        </is>
+      </c>
+      <c r="L34" s="7" t="inlineStr">
+        <is>
+          <t>Cramer-Krasselt, BVK, Hoffman York</t>
+        </is>
+      </c>
+      <c r="M34" s="7" t="inlineStr">
+        <is>
           <t>I-94 / I-43 corridors; Lamar-dominant plus regional Ohio/Wisconsin operators.</t>
         </is>
       </c>
@@ -55433,6 +55943,21 @@
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
+          <t>WSYX 6 · WBNS 10 · WCMH 4 · WTTE Fox 28</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="inlineStr">
+        <is>
+          <t>iHeart (WTVN/WNCI) · Saga (WSNY) · Urban One</t>
+        </is>
+      </c>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>Fahlgren Mortine, The Shipyard, Ologie</t>
+        </is>
+      </c>
+      <c r="M35" s="7" t="inlineStr">
+        <is>
           <t>~2,200 boards; one of the Midwest's deepest OOH inventories (OAA of Ohio HQ'd here).</t>
         </is>
       </c>
@@ -55479,6 +56004,21 @@
       </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
+          <t>KMBC 9 · KCTV 5 · KSHB 41 · WDAF Fox 4</t>
+        </is>
+      </c>
+      <c r="K36" s="7" t="inlineStr">
+        <is>
+          <t>Audacy (KMBZ) · Cumulus · Carter Broadcast (KPRS)</t>
+        </is>
+      </c>
+      <c r="L36" s="7" t="inlineStr">
+        <is>
+          <t>VML (HQ), Barkley OKRP</t>
+        </is>
+      </c>
+      <c r="M36" s="7" t="inlineStr">
+        <is>
           <t>I-35/I-70; Ad-Trend the largest locally owned operator (since 1985).</t>
         </is>
       </c>
@@ -55525,6 +56065,21 @@
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
+          <t>WKRN 2 · WTVF 5 · WSMV 4 · WZTV Fox 17</t>
+        </is>
+      </c>
+      <c r="K37" s="7" t="inlineStr">
+        <is>
+          <t>iHeart (WLAC) · Cumulus (WKDF/WSM-FM) · Opry Ent. (WSM-AM)</t>
+        </is>
+      </c>
+      <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>bohan, GS&amp;F</t>
+        </is>
+      </c>
+      <c r="M37" s="7" t="inlineStr">
+        <is>
           <t>I-40 / I-24 / I-65 and Broadway/tourism demand; Allison Outdoor active regionally.</t>
         </is>
       </c>
@@ -55571,6 +56126,21 @@
       </c>
       <c r="J38" s="7" t="inlineStr">
         <is>
+          <t>KTVX 4 · KUTV 2 · KSL 5 · KSTU Fox 13</t>
+        </is>
+      </c>
+      <c r="K38" s="7" t="inlineStr">
+        <is>
+          <t>Bonneville (HQ — KSL) · iHeart · Broadway Media (local)</t>
+        </is>
+      </c>
+      <c r="L38" s="7" t="inlineStr">
+        <is>
+          <t>Struck, Love Communications, Richter7</t>
+        </is>
+      </c>
+      <c r="M38" s="7" t="inlineStr">
+        <is>
           <t>I-15 corridor; Reagan Outdoor (HQ) &amp; YESCO dominate; billboards politically restricted.</t>
         </is>
       </c>
@@ -55617,6 +56187,21 @@
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
+          <t>WGNO 26 · WWL 4 · WDSU 6 · WVUE Fox 8</t>
+        </is>
+      </c>
+      <c r="K39" s="7" t="inlineStr">
+        <is>
+          <t>Audacy (WWL radio) · iHeart · Cumulus</t>
+        </is>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>Peter Mayer, Trumpet</t>
+        </is>
+      </c>
+      <c r="M39" s="7" t="inlineStr">
+        <is>
           <t>I-10 / French Quarter &amp; tourism demand; Lamar (Louisiana roots) &amp; Lindmark strong.</t>
         </is>
       </c>
@@ -55663,6 +56248,21 @@
       </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
+          <t>KOCO 5 · KWTV 9 · KFOR 4 · KOKH Fox 25</t>
+        </is>
+      </c>
+      <c r="K40" s="7" t="inlineStr">
+        <is>
+          <t>iHeart (KTOK) · Cumulus (KATT) · Tyler Media (local)</t>
+        </is>
+      </c>
+      <c r="L40" s="7" t="inlineStr">
+        <is>
+          <t>Ackerman McQueen, VI Marketing + Branding</t>
+        </is>
+      </c>
+      <c r="M40" s="7" t="inlineStr">
+        <is>
           <t>I-35 / I-40 / I-44; Lindmark, Headrick and BM cover Oklahoma broadly.</t>
         </is>
       </c>
@@ -55709,6 +56309,21 @@
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
+          <t>WATN 24 · WREG 3 · WMC 5 · WHBQ Fox 13</t>
+        </is>
+      </c>
+      <c r="K41" s="7" t="inlineStr">
+        <is>
+          <t>iHeart · Cumulus · Flinn Broadcasting (local)</t>
+        </is>
+      </c>
+      <c r="L41" s="7" t="inlineStr">
+        <is>
+          <t>archer malmo (Signet), Sullivan Branding</t>
+        </is>
+      </c>
+      <c r="M41" s="7" t="inlineStr">
+        <is>
           <t>I-40 / I-55 freight corridors; Lamar-dominant plus Allison Outdoor regionally.</t>
         </is>
       </c>
@@ -55755,6 +56370,21 @@
       </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
+          <t>WRIC 8 · WTVR 6 · WWBT 12 · WRLH Fox 35</t>
+        </is>
+      </c>
+      <c r="K42" s="7" t="inlineStr">
+        <is>
+          <t>Audacy (WRVA) · SummitMedia · Urban One</t>
+        </is>
+      </c>
+      <c r="L42" s="7" t="inlineStr">
+        <is>
+          <t>The Martin Agency (GEICO), Arts &amp; Letters</t>
+        </is>
+      </c>
+      <c r="M42" s="7" t="inlineStr">
+        <is>
           <t>I-95 / I-64 corridors; Lamar &amp; OUTFRONT dominant in a supply-limited market.</t>
         </is>
       </c>
@@ -55801,6 +56431,21 @@
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
+          <t>KVUE 24 · KEYE 42 · KXAN 36 · KTBC Fox 7</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
+          <t>iHeart · Audacy · Waterloo Media (local — KLBJ)</t>
+        </is>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
+        <is>
+          <t>GSD&amp;M (HQ), McGarrah Jessee, Preacher</t>
+        </is>
+      </c>
+      <c r="M43" s="7" t="inlineStr">
+        <is>
           <t>Reagan Outdoor-dominated; tech-driven demand along I-35 / MoPac / US-183.</t>
         </is>
       </c>
@@ -55847,14 +56492,29 @@
       </c>
       <c r="J44" s="7" t="inlineStr">
         <is>
+          <t>WJXX 25 · WJAX 47 · WTLV 12 · WFOX 30</t>
+        </is>
+      </c>
+      <c r="K44" s="7" t="inlineStr">
+        <is>
+          <t>Cox (WOKV/WAPE) · iHeart</t>
+        </is>
+      </c>
+      <c r="L44" s="7" t="inlineStr">
+        <is>
+          <t>Dalton Agency, Shepherd (St. John &amp; Partners)</t>
+        </is>
+      </c>
+      <c r="M44" s="7" t="inlineStr">
+        <is>
           <t>Largest US city by land area; I-95 / I-295 corridors carry the value.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:J44"/>
+  <autoFilter ref="A2:M44"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -63894,6 +64554,1995 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>US QUICK-START BY METRO - WHO TO CALL IN EACH MARKET</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Metro</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Metro Pop</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>OOH Rate Band</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Top Local OOH Operators</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>Big-4 TV</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Radio Groups</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Newspaper</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Agencies to Call</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>19.9M</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>$3,000-$50,000/mo</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>JCDecaux, Branded Cities Network, Brooklyn Outdoor</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>WABC 7 · WCBS 2 · WNBC 4 · WNYW Fox 5</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Audacy (WFAN, 1010 WINS) · iHeart (Z100) · SBS (Spanish, HQ)</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>The New York Times / NY Post / Daily News</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>Ogilvy, BBDO, Droga5, McCann (global HQs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>13.0M</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>$2,500-$40,000/mo</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>JCDecaux, Regency Outdoor Advertising, Branded Cities Network</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>KABC 7 · KCBS 2 · KNBC 4 · KTTV Fox 11</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>iHeart (KIIS, KFI) · Audacy (KROQ, KNX) · Univision/SBS (Spanish)</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>Los Angeles Times</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>Deutsch LA, 72andSunny, TBWA\Chiat\Day</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>9.4M</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>$2,000-$25,000/mo</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>JCDecaux, Becker Boards, Branded Cities Network</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>WLS 7 · WBBM 2 · WMAQ 5 · WFLD Fox 32</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Audacy (WBBM, WSCR) · iHeart · Nexstar (WGN Radio)</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Chicago Tribune / Sun-Times</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Leo Burnett, FCB Chicago, Energy BBDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>4.6M (Bay CSA ~9.7M)</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>$2,500-$30,000/mo</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Becker Boards</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>KGO 7 · KPIX 5 · KNTV 11 · KTVU Fox 2</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Audacy (KCBS) · iHeart · Bonneville</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>San Francisco Chronicle</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>Goodby Silverstein, Duncan Channon, Argonaut</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>6.4M</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>$1,500-$16,000/mo</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>Adams Outdoor Advertising, Billboard Company Atlanta, Trailhead Media</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>WSB 2 · WANF 46 · WXIA 11 · WAGA Fox 5</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Cox Media Group (HQ, WSB) · iHeart · Urban One</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>The Atlanta Journal-Constitution</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>22squared, Dagger, Chemistry</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Washington DC</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>6.3M</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>$2,000-$20,000/mo</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Capitol Outdoor, Digital Outdoor Advertising, LLC, Digital Outdoor Advertising — DC</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>WJLA 7 · WUSA 9 · WRC 4 · WTTG Fox 5</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>Hubbard (WTOP — top-billing US station) · iHeart · Cumulus (WMAL)</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>The Washington Post</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>GMMB (political), RP3 Agency</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>4.9M</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>$1,800-$18,000/mo</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>Digital Outdoor Advertising, LLC</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>WCVB 5 · WBZ 4 · WBTS 10 · WFXT Fox 25</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>iHeart (WBZ-AM) · Audacy (WEEI) · Beasley</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>The Boston Globe</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Hill Holliday, Arnold, MullenLowe, Allen &amp; Gerritsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>8.1M</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>$1,500-$18,000/mo</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>SignAd Outdoor Advertising, Arrington Outdoor Advertising, Lux Media</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>WFAA 8 · KTVT 11 · KXAS 5 · KDFW Fox 4</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>iHeart · Audacy (KRLD) · Cumulus (WBAP)</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>The Dallas Morning News</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>TRG (The Richards Group), Dieste (Hispanic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>7.5M</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>$1,500-$15,000/mo</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>SignAd Outdoor Advertising, Gilbreath Outdoor Advertising, Lux Media</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>KTRK 13 · KHOU 11 · KPRC 2 · KRIV Fox 26</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>iHeart (KTRH) · Audacy · Cox (KKBQ)</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>Houston Chronicle</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Lopez Negrete (Hispanic), MMI Agency</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Miami</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>6.2M</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>$1,800-$20,000/mo</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Becker Boards, Capitol Outdoor, Carter Outdoor Advertising</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>WPLG 10 · WFOR 4 · WTVJ 6 · WSVN Fox 7</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>iHeart · Cox · SBS (Spanish broadcasting HQ)</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>Miami Herald</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>Zimmerman, Crispin (legacy), República Havas (Hispanic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>6.2M</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>$1,500-$12,000/mo</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>Capitol Outdoor, Digital Outdoor Advertising, LLC, Intersection</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>WPVI 6 · KYW 3 · WCAU 10 · WTXF Fox 29</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Audacy (HQ — KYW, WIP) · iHeart · Beasley (WMMR)</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>The Philadelphia Inquirer</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Digitas Philly (legacy), Brownstein Group, LevLane</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Detroit</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>4.3M</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>$1,200-$12,000/mo</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>International Outdoor</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>WXYZ 7 · WWJ 62 · WDIV 4 · WJBK Fox 2</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>Audacy (WWJ, WXYT) · iHeart · Cumulus (WJR)</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>Detroit Free Press / The Detroit News</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>Doner, Campbell Ewald, Lafayette American</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>4.0M</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>$1,500-$14,000/mo</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>Pacific Outdoor Advertising, Parker Outdoor Inc., Summus Outdoor</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>KOMO 4 · KIRO 7 · KING 5 · KCPQ Fox 13</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>Bonneville (KIRO) · iHeart · Audacy</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>The Seattle Times</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>Wongdoody, Copacino Fujikado, DNA</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Minneapolis</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>3.7M</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>$1,200-$12,000/mo</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>Franklin Outdoor Advertising, Blue Ox Media</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>KSTP 5 · WCCO 4 · KARE 11 · KMSP Fox 9</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>Hubbard (HQ — KSTP, KS95) · iHeart (KFAN) · Audacy (WCCO)</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>Star Tribune</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>Fallon, Colle McVoy, Periscope</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>5.1M</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>$1,200-$10,000/mo</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>American Outdoor Advertising, Arizona Billboard Company, Becker Boards</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>KNXV 15 · KPHO 5 · KPNX 12 · KSAZ Fox 10</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>Bonneville (KTAR) · iHeart · Hubbard</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>The Arizona Republic</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>OH Partners, LaneTerralever, Zion &amp; Zion</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Tampa</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>3.3M</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>$1,200-$11,000/mo</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>Tampa Outdoor Advertising, Logan Outdoor Advertising, Signal Outdoor Advertising</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>WFTS 28 · WTSP 10 · WFLA 8 · WTVT Fox 13</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>iHeart (WFLA-AM) · Cox · Beasley (WQYK)</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>Tampa Bay Times</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>PPK, Schifino Lee</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>3.0M</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>$1,200-$11,000/mo</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>Mile High Outdoor, Elevation Outdoor Advertising, Outdoor Ads, Inc.</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>KMGH 7 · KCNC 4 · KUSA 9 · KDVR Fox 31</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>iHeart (KOA) · Bonneville (KYGO/KOSI) · Audacy</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>The Denver Post</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Karsh Hagan, Cactus, Grit Advertising</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Cleveland</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>2.2M</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>$1,000-$11,000/mo</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>American Outdoor Advertising (Columbus), Outdoor Advertising Center, Key-Ads, Inc.</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>WEWS 5 · WOIO 19 · WKYC 3 · WJW Fox 8</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>iHeart (WTAM) · Audacy · Good Karma (WKNR)</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>The Plain Dealer / cleveland.com</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>Marcus Thomas, Adcom, Falls</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Sacramento</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>2.4M</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>$1,200-$11,000/mo</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>Capitol Outdoor</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>KXTV 10 · KOVR 13 · KCRA 3 · KTXL Fox 40</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>iHeart (KFBK) · Audacy · Bonneville</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>The Sacramento Bee</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>The Glass Agency, Position Interactive</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Orlando</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>2.8M</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>$1,200-$12,000/mo</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>Orlando Outdoor</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>WFTV 9 · WKMG 6 · WESH 2 · WOFL Fox 35</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>iHeart · Cox (WDBO)</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>Orlando Sentinel</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>&amp;Barr, PUSH</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>St. Louis</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>2.8M</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>$1,000-$10,000/mo</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>DDI Media, Robinson Outdoor</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>KDNL 30 · KMOV 4 · KSDK 5 · KTVI Fox 2</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>Audacy (KMOX) · iHeart · Hubbard</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>St. Louis Post-Dispatch</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>HLK, Rodgers Townsend (DDB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Pittsburgh</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>2.4M</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>$1,000-$9,000/mo</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>Penneco Outdoor Advertising, Steel City Billboards, TM Advertising</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>WTAE 4 · KDKA 2 · WPXI 11 · WPGH Fox 53</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>Audacy (KDKA) · iHeart (WDVE) · Steel City Media</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>Pittsburgh Post-Gazette</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>Brunner, MARC USA (legacy), Gatesman</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>3.3M</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>$1,500-$10,000/mo</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>American Outdoor Advertising, Capitol Outdoor, Bray Outdoor Ads</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>KGTV 10 · KFMB 8 · KNSD 7/39 · KSWB Fox 5</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>iHeart (KOGO) · Audacy · Local Media San Diego</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>The San Diego Union-Tribune</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>VITRO (Petco work), i.d.e.a.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Baltimore</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>2.8M</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>$1,200-$11,000/mo</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>Vision Outdoor</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>WMAR 2 · WJZ 13 · WBAL 11 · WBFF Fox 45</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>Hearst (WBAL radio) · iHeart · Audacy</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>The Baltimore Sun</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>Planit, GKV, idfive</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>2.8M</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>$1,000-$9,000/mo</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>Allison Outdoor Advertising, Adams Outdoor Advertising, Trailhead Media</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>WSOC 9 · WBTV 3 · WCNC 36 · WJZY Fox 46</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>iHeart · Urban One · Norsan Media (Spanish, local)</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>The Charlotte Observer</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Wray Ward, Luquire</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Raleigh</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>1.5M (Triangle ~2.1M)</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>$1,000-$10,000/mo</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>Allison Outdoor Advertising, Adams Outdoor Advertising, Trailhead Media</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>WTVD 11 · WNCN 17 · WRAL 5 · WRAZ Fox 50</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>iHeart · Curtis Media (local Triangle) · Capitol Broadcasting</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>The News &amp; Observer</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>McKinney (Durham), Baldwin&amp;</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Indianapolis</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>2.1M</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>$1,000-$10,000/mo</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>Reagan Outdoor Advertising, Keyes Outdoor Advertising</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>WRTV 6 · WTTV 4 · WTHR 13 · WXIN Fox 59</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>iHeart · Cumulus (WFMS) · Urban One</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>The Indianapolis Star</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>Young &amp; Laramore, Hirons</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Cincinnati</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>2.3M</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>$1,000-$10,000/mo</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>American Outdoor Advertising (Columbus), Outdoor Advertising Center, Key-Ads, Inc.</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>WCPO 9 · WKRC 12 · WLWT 5 · WXIX Fox 19</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>iHeart (700WLW) · Hubbard (WKRQ) · Cumulus</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>The Cincinnati Enquirer</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>Curiosity, Barefoot Proximity (BBDO)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Las Vegas</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>2.3M</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>$1,500-$25,000/mo</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>Reagan Outdoor Advertising, Las Vegas Billboards</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>KTNV 13 · KLAS 8 · KSNV 3 · KVVU Fox 5</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>Audacy · iHeart · Lotus (local)</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>Las Vegas Review-Journal</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>R&amp;R Partners ('What happens here, stays here')</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>San Antonio</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>$1,000-$8,000/mo</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>SignAd Outdoor Advertising, Gilbreath Outdoor Advertising, Lux Media</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>KSAT 12 · KENS 5 · WOAI 4 · KABB Fox 29</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>iHeartMedia (corporate HQ — WOAI) · Cox · Univision (Spanish)</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>San Antonio Express-News</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>The Atkins Group, Giles-Parscale (legacy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Portland</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>$1,200-$11,000/mo</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>Grapevine Outdoor, New Tradition Media, Meadow Outdoor Advertising</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>KATU 2 · KOIN 6 · KGW 8 · KPTV Fox 12</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>iHeart (KEX) · Audacy · Alpha Media (HQ Portland)</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>The Oregonian</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>Wieden+Kennedy (HQ), Instrument, Opinionated</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Milwaukee</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>1.6M</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>$1,000-$10,000/mo</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>Outdoor Advertising Center</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>WISN 12 · WDJT 58 · WTMJ 4 · WITI Fox 6</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>Good Karma (WTMJ radio) · iHeart · Saga (WKLH)</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>Milwaukee Journal Sentinel</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>Cramer-Krasselt, BVK, Hoffman York</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Columbus</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>2.2M</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>$1,000-$9,000/mo</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>American Outdoor Advertising (Columbus), Outdoor Advertising Center, Kenjoh Outdoor</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>WSYX 6 · WBNS 10 · WCMH 4 · WTTE Fox 28</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>iHeart (WTVN/WNCI) · Saga (WSNY) · Urban One</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>The Columbus Dispatch</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>Fahlgren Mortine, The Shipyard, Ologie</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>Kansas City</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>2.2M</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>$1,000-$9,000/mo</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>Ad-Trend, Midwest Billboards</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>KMBC 9 · KCTV 5 · KSHB 41 · WDAF Fox 4</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>Audacy (KMBZ) · Cumulus · Carter Broadcast (KPRS)</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>The Kansas City Star</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>VML (HQ), Barkley OKRP</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Nashville</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>2.1M</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>$1,200-$11,000/mo</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>Allison Outdoor Advertising</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>WKRN 2 · WTVF 5 · WSMV 4 · WZTV Fox 17</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>iHeart (WLAC) · Cumulus (WKDF/WSM-FM) · Opry Ent. (WSM-AM)</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>The Tennessean</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>bohan, GS&amp;F</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Salt Lake City</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>1.3M</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>$1,000-$9,000/mo</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>Reagan Outdoor Advertising, YESCO Outdoor Media</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>KTVX 4 · KUTV 2 · KSL 5 · KSTU Fox 13</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>Bonneville (HQ — KSL) · iHeart · Broadway Media (local)</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>The Salt Lake Tribune / Deseret News</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>Struck, Love Communications, Richter7</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>New Orleans</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>1.3M</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>$1,000-$11,000/mo</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>Lindmark Outdoor Media</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>WGNO 26 · WWL 4 · WDSU 6 · WVUE Fox 8</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>Audacy (WWL radio) · iHeart · Cumulus</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>The Times-Picayune / NOLA.com / The Advocate</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>Peter Mayer, Trumpet</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Oklahoma City</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>$900-$8,000/mo</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>Headrick Outdoor Media, Lindmark Outdoor Media</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>KOCO 5 · KWTV 9 · KFOR 4 · KOKH Fox 25</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>iHeart (KTOK) · Cumulus (KATT) · Tyler Media (local)</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>The Oklahoman</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>Ackerman McQueen, VI Marketing + Branding</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Memphis</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>1.3M</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>$900-$8,000/mo</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>Allison Outdoor Advertising</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>WATN 24 · WREG 3 · WMC 5 · WHBQ Fox 13</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>iHeart · Cumulus · Flinn Broadcasting (local)</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>The Commercial Appeal</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>archer malmo (Signet), Sullivan Branding</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>1.3M</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>$900-$8,000/mo</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>Lamar / Clear Channel / OUTFRONT</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>WRIC 8 · WTVR 6 · WWBT 12 · WRLH Fox 35</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>Audacy (WRVA) · SummitMedia · Urban One</t>
+        </is>
+      </c>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>Richmond Times-Dispatch</t>
+        </is>
+      </c>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>The Martin Agency (GEICO), Arts &amp; Letters</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>$1,200-$12,000/mo</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>Reagan Outdoor Advertising, Lux Media, Burkett Media</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>KVUE 24 · KEYE 42 · KXAN 36 · KTBC Fox 7</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>iHeart · Audacy · Waterloo Media (local — KLBJ)</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>Austin American-Statesman</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>GSD&amp;M (HQ), McGarrah Jessee, Preacher</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Jacksonville</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>1.7M</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>$800-$6,000/mo</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>Digital Outdoor Advertising, LLC, American Mobile Ads, Daily Billboards</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>WJXX 25 · WJAX 47 · WTLV 12 · WFOX 30</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>Cox (WOKV/WAPE) · iHeart</t>
+        </is>
+      </c>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>The Florida Times-Union</t>
+        </is>
+      </c>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>Dalton Agency, Shepherd (St. John &amp; Partners)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>UNIVERSAL FOUNDATION (every metro, before any media buy): 1) Google Business Profile + Local Services Ads + review engine  2) City landing pages + local SEO  3) Geofenced social + search ads + retargeting  4) Then buy local media below.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:I44"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A46:I46"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
